--- a/src/data/processed/hpc1826.xlsx
+++ b/src/data/processed/hpc1826.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,31 +29,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>Cement</t>
+    <t>Cem</t>
   </si>
   <si>
-    <t>Slag</t>
+    <t>Slg</t>
   </si>
   <si>
-    <t>FlyAsh</t>
+    <t>FA</t>
   </si>
   <si>
-    <t>Water</t>
+    <t>Wat</t>
   </si>
   <si>
-    <t>W_B</t>
+    <t>W/B</t>
   </si>
   <si>
-    <t>W_C</t>
+    <t>W/C</t>
   </si>
   <si>
-    <t>SP_C</t>
+    <t>SP/C</t>
   </si>
   <si>
-    <t>CoarseAgg</t>
+    <t>CA</t>
   </si>
   <si>
-    <t>FineAgg</t>
+    <t>FAgg</t>
   </si>
   <si>
     <t>Age</t>
@@ -1053,13 +1053,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K1926"/>
+  <dimension ref="A1:K1827"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="3" width="12.8181818181818"/>
-    <col min="7" max="7" width="12.8181818181818"/>
-    <col min="11" max="11" width="12.8181818181818"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
@@ -64868,3607 +64863,142 @@
     </row>
     <row r="1824" spans="1:11">
       <c r="A1824">
-        <v>273</v>
+        <v>146</v>
       </c>
       <c r="B1824">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="C1824">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D1824">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="E1824">
-        <v>0.456521739130435</v>
+        <v>0.592592592592593</v>
       </c>
       <c r="F1824">
-        <v>0.769230769230769</v>
+        <v>1.31506849315069</v>
       </c>
       <c r="G1824">
-        <v>0.032967032967033</v>
+        <v>0.0753424657534247</v>
       </c>
       <c r="H1824">
-        <v>904</v>
+        <v>961</v>
       </c>
       <c r="I1824">
-        <v>680</v>
+        <v>749</v>
       </c>
       <c r="J1824">
         <v>28</v>
       </c>
       <c r="K1824">
-        <v>34.99</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="1825" spans="1:11">
       <c r="A1825">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="B1825">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="C1825">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="D1825">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E1825">
-        <v>0.357852882703777</v>
+        <v>0.422594142259414</v>
       </c>
       <c r="F1825">
-        <v>1.10429447852761</v>
+        <v>0.737226277372263</v>
       </c>
       <c r="G1825">
-        <v>0.0736196319018405</v>
+        <v>0.0328467153284671</v>
       </c>
       <c r="H1825">
-        <v>843</v>
+        <v>759</v>
       </c>
       <c r="I1825">
-        <v>746</v>
+        <v>827</v>
       </c>
       <c r="J1825">
         <v>28</v>
       </c>
       <c r="K1825">
-        <v>41.14</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="1826" spans="1:11">
       <c r="A1826">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="B1826">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C1826">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="D1826">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="E1826">
-        <v>0.357285429141717</v>
+        <v>0.453237410071943</v>
       </c>
       <c r="F1826">
-        <v>1.10493827160494</v>
+        <v>0.615635179153095</v>
       </c>
       <c r="G1826">
-        <v>0.0987654320987654</v>
+        <v>0.0325732899022801</v>
       </c>
       <c r="H1826">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="I1826">
-        <v>743</v>
+        <v>765</v>
       </c>
       <c r="J1826">
         <v>28</v>
       </c>
       <c r="K1826">
-        <v>41.81</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="1827" spans="1:11">
       <c r="A1827">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="B1827">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="C1827">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="D1827">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="E1827">
-        <v>0.358</v>
+        <v>0.457858769931663</v>
       </c>
       <c r="F1827">
-        <v>1.10493827160494</v>
+        <v>0.770114942528736</v>
       </c>
       <c r="G1827">
-        <v>0.117283950617284</v>
+        <v>0.0344827586206896</v>
       </c>
       <c r="H1827">
-        <v>838</v>
+        <v>864</v>
       </c>
       <c r="I1827">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="J1827">
         <v>28</v>
       </c>
       <c r="K1827">
-        <v>42.08</v>
-      </c>
-    </row>
-    <row r="1828" spans="1:11">
-      <c r="A1828">
-        <v>154</v>
-      </c>
-      <c r="B1828">
-        <v>112</v>
-      </c>
-      <c r="C1828">
-        <v>144</v>
-      </c>
-      <c r="D1828">
-        <v>220</v>
-      </c>
-      <c r="E1828">
-        <v>0.536585365853659</v>
-      </c>
-      <c r="F1828">
-        <v>1.42857142857143</v>
-      </c>
-      <c r="G1828">
-        <v>0.0649350649350649</v>
-      </c>
-      <c r="H1828">
-        <v>923</v>
-      </c>
-      <c r="I1828">
-        <v>658</v>
-      </c>
-      <c r="J1828">
-        <v>28</v>
-      </c>
-      <c r="K1828">
-        <v>26.82</v>
-      </c>
-    </row>
-    <row r="1829" spans="1:11">
-      <c r="A1829">
-        <v>147</v>
-      </c>
-      <c r="B1829">
-        <v>89</v>
-      </c>
-      <c r="C1829">
-        <v>115</v>
-      </c>
-      <c r="D1829">
-        <v>202</v>
-      </c>
-      <c r="E1829">
-        <v>0.575498575498576</v>
-      </c>
-      <c r="F1829">
-        <v>1.37414965986395</v>
-      </c>
-      <c r="G1829">
-        <v>0.0612244897959184</v>
-      </c>
-      <c r="H1829">
-        <v>860</v>
-      </c>
-      <c r="I1829">
-        <v>829</v>
-      </c>
-      <c r="J1829">
-        <v>28</v>
-      </c>
-      <c r="K1829">
-        <v>25.21</v>
-      </c>
-    </row>
-    <row r="1830" spans="1:11">
-      <c r="A1830">
-        <v>152</v>
-      </c>
-      <c r="B1830">
-        <v>139</v>
-      </c>
-      <c r="C1830">
-        <v>178</v>
-      </c>
-      <c r="D1830">
-        <v>168</v>
-      </c>
-      <c r="E1830">
-        <v>0.358208955223881</v>
-      </c>
-      <c r="F1830">
-        <v>1.10526315789474</v>
-      </c>
-      <c r="G1830">
-        <v>0.118421052631579</v>
-      </c>
-      <c r="H1830">
-        <v>944</v>
-      </c>
-      <c r="I1830">
-        <v>695</v>
-      </c>
-      <c r="J1830">
-        <v>28</v>
-      </c>
-      <c r="K1830">
-        <v>38.86</v>
-      </c>
-    </row>
-    <row r="1831" spans="1:11">
-      <c r="A1831">
-        <v>145</v>
-      </c>
-      <c r="B1831">
-        <v>0</v>
-      </c>
-      <c r="C1831">
-        <v>227</v>
-      </c>
-      <c r="D1831">
-        <v>240</v>
-      </c>
-      <c r="E1831">
-        <v>0.645161290322581</v>
-      </c>
-      <c r="F1831">
-        <v>1.6551724137931</v>
-      </c>
-      <c r="G1831">
-        <v>0.0413793103448276</v>
-      </c>
-      <c r="H1831">
-        <v>750</v>
-      </c>
-      <c r="I1831">
-        <v>853</v>
-      </c>
-      <c r="J1831">
-        <v>28</v>
-      </c>
-      <c r="K1831">
-        <v>36.59</v>
-      </c>
-    </row>
-    <row r="1832" spans="1:11">
-      <c r="A1832">
-        <v>152</v>
-      </c>
-      <c r="B1832">
-        <v>0</v>
-      </c>
-      <c r="C1832">
-        <v>237</v>
-      </c>
-      <c r="D1832">
-        <v>204</v>
-      </c>
-      <c r="E1832">
-        <v>0.524421593830334</v>
-      </c>
-      <c r="F1832">
-        <v>1.34210526315789</v>
-      </c>
-      <c r="G1832">
-        <v>0.0394736842105263</v>
-      </c>
-      <c r="H1832">
-        <v>785</v>
-      </c>
-      <c r="I1832">
-        <v>892</v>
-      </c>
-      <c r="J1832">
-        <v>28</v>
-      </c>
-      <c r="K1832">
-        <v>32.71</v>
-      </c>
-    </row>
-    <row r="1833" spans="1:11">
-      <c r="A1833">
-        <v>304</v>
-      </c>
-      <c r="B1833">
-        <v>0</v>
-      </c>
-      <c r="C1833">
-        <v>140</v>
-      </c>
-      <c r="D1833">
-        <v>214</v>
-      </c>
-      <c r="E1833">
-        <v>0.481981981981982</v>
-      </c>
-      <c r="F1833">
-        <v>0.703947368421053</v>
-      </c>
-      <c r="G1833">
-        <v>0.0197368421052632</v>
-      </c>
-      <c r="H1833">
-        <v>895</v>
-      </c>
-      <c r="I1833">
-        <v>722</v>
-      </c>
-      <c r="J1833">
-        <v>28</v>
-      </c>
-      <c r="K1833">
-        <v>38.46</v>
-      </c>
-    </row>
-    <row r="1834" spans="1:11">
-      <c r="A1834">
-        <v>145</v>
-      </c>
-      <c r="B1834">
-        <v>106</v>
-      </c>
-      <c r="C1834">
-        <v>136</v>
-      </c>
-      <c r="D1834">
-        <v>208</v>
-      </c>
-      <c r="E1834">
-        <v>0.537467700258398</v>
-      </c>
-      <c r="F1834">
-        <v>1.43448275862069</v>
-      </c>
-      <c r="G1834">
-        <v>0.0689655172413793</v>
-      </c>
-      <c r="H1834">
-        <v>751</v>
-      </c>
-      <c r="I1834">
-        <v>883</v>
-      </c>
-      <c r="J1834">
-        <v>28</v>
-      </c>
-      <c r="K1834">
-        <v>26.02</v>
-      </c>
-    </row>
-    <row r="1835" spans="1:11">
-      <c r="A1835">
-        <v>148</v>
-      </c>
-      <c r="B1835">
-        <v>109</v>
-      </c>
-      <c r="C1835">
-        <v>139</v>
-      </c>
-      <c r="D1835">
-        <v>193</v>
-      </c>
-      <c r="E1835">
-        <v>0.487373737373737</v>
-      </c>
-      <c r="F1835">
-        <v>1.30405405405405</v>
-      </c>
-      <c r="G1835">
-        <v>0.0472972972972973</v>
-      </c>
-      <c r="H1835">
-        <v>768</v>
-      </c>
-      <c r="I1835">
-        <v>902</v>
-      </c>
-      <c r="J1835">
-        <v>28</v>
-      </c>
-      <c r="K1835">
-        <v>28.03</v>
-      </c>
-    </row>
-    <row r="1836" spans="1:11">
-      <c r="A1836">
-        <v>142</v>
-      </c>
-      <c r="B1836">
-        <v>130</v>
-      </c>
-      <c r="C1836">
-        <v>167</v>
-      </c>
-      <c r="D1836">
-        <v>215</v>
-      </c>
-      <c r="E1836">
-        <v>0.489749430523918</v>
-      </c>
-      <c r="F1836">
-        <v>1.51408450704225</v>
-      </c>
-      <c r="G1836">
-        <v>0.0422535211267606</v>
-      </c>
-      <c r="H1836">
-        <v>735</v>
-      </c>
-      <c r="I1836">
-        <v>836</v>
-      </c>
-      <c r="J1836">
-        <v>28</v>
-      </c>
-      <c r="K1836">
-        <v>31.37</v>
-      </c>
-    </row>
-    <row r="1837" spans="1:11">
-      <c r="A1837">
-        <v>354</v>
-      </c>
-      <c r="B1837">
-        <v>0</v>
-      </c>
-      <c r="C1837">
-        <v>0</v>
-      </c>
-      <c r="D1837">
-        <v>234</v>
-      </c>
-      <c r="E1837">
-        <v>0.661016949152542</v>
-      </c>
-      <c r="F1837">
-        <v>0.661016949152542</v>
-      </c>
-      <c r="G1837">
-        <v>0.0169491525423729</v>
-      </c>
-      <c r="H1837">
-        <v>959</v>
-      </c>
-      <c r="I1837">
-        <v>691</v>
-      </c>
-      <c r="J1837">
-        <v>28</v>
-      </c>
-      <c r="K1837">
-        <v>33.91</v>
-      </c>
-    </row>
-    <row r="1838" spans="1:11">
-      <c r="A1838">
-        <v>374</v>
-      </c>
-      <c r="B1838">
-        <v>0</v>
-      </c>
-      <c r="C1838">
-        <v>0</v>
-      </c>
-      <c r="D1838">
-        <v>190</v>
-      </c>
-      <c r="E1838">
-        <v>0.508021390374332</v>
-      </c>
-      <c r="F1838">
-        <v>0.508021390374332</v>
-      </c>
-      <c r="G1838">
-        <v>0.018716577540107</v>
-      </c>
-      <c r="H1838">
-        <v>1013</v>
-      </c>
-      <c r="I1838">
-        <v>730</v>
-      </c>
-      <c r="J1838">
-        <v>28</v>
-      </c>
-      <c r="K1838">
-        <v>32.44</v>
-      </c>
-    </row>
-    <row r="1839" spans="1:11">
-      <c r="A1839">
-        <v>159</v>
-      </c>
-      <c r="B1839">
-        <v>116</v>
-      </c>
-      <c r="C1839">
-        <v>149</v>
-      </c>
-      <c r="D1839">
-        <v>175</v>
-      </c>
-      <c r="E1839">
-        <v>0.412735849056604</v>
-      </c>
-      <c r="F1839">
-        <v>1.10062893081761</v>
-      </c>
-      <c r="G1839">
-        <v>0.0943396226415094</v>
-      </c>
-      <c r="H1839">
-        <v>953</v>
-      </c>
-      <c r="I1839">
-        <v>720</v>
-      </c>
-      <c r="J1839">
-        <v>28</v>
-      </c>
-      <c r="K1839">
-        <v>34.05</v>
-      </c>
-    </row>
-    <row r="1840" spans="1:11">
-      <c r="A1840">
-        <v>153</v>
-      </c>
-      <c r="B1840">
-        <v>0</v>
-      </c>
-      <c r="C1840">
-        <v>239</v>
-      </c>
-      <c r="D1840">
-        <v>200</v>
-      </c>
-      <c r="E1840">
-        <v>0.510204081632653</v>
-      </c>
-      <c r="F1840">
-        <v>1.30718954248366</v>
-      </c>
-      <c r="G1840">
-        <v>0.0392156862745098</v>
-      </c>
-      <c r="H1840">
-        <v>1002</v>
-      </c>
-      <c r="I1840">
-        <v>684</v>
-      </c>
-      <c r="J1840">
-        <v>28</v>
-      </c>
-      <c r="K1840">
-        <v>28.29</v>
-      </c>
-    </row>
-    <row r="1841" spans="1:11">
-      <c r="A1841">
-        <v>295</v>
-      </c>
-      <c r="B1841">
-        <v>106</v>
-      </c>
-      <c r="C1841">
-        <v>136</v>
-      </c>
-      <c r="D1841">
-        <v>206</v>
-      </c>
-      <c r="E1841">
-        <v>0.383612662942272</v>
-      </c>
-      <c r="F1841">
-        <v>0.698305084745763</v>
-      </c>
-      <c r="G1841">
-        <v>0.0372881355932203</v>
-      </c>
-      <c r="H1841">
-        <v>750</v>
-      </c>
-      <c r="I1841">
-        <v>766</v>
-      </c>
-      <c r="J1841">
-        <v>28</v>
-      </c>
-      <c r="K1841">
-        <v>41.01</v>
-      </c>
-    </row>
-    <row r="1842" spans="1:11">
-      <c r="A1842">
-        <v>310</v>
-      </c>
-      <c r="B1842">
-        <v>0</v>
-      </c>
-      <c r="C1842">
-        <v>143</v>
-      </c>
-      <c r="D1842">
-        <v>168</v>
-      </c>
-      <c r="E1842">
-        <v>0.370860927152318</v>
-      </c>
-      <c r="F1842">
-        <v>0.541935483870968</v>
-      </c>
-      <c r="G1842">
-        <v>0.032258064516129</v>
-      </c>
-      <c r="H1842">
-        <v>914</v>
-      </c>
-      <c r="I1842">
-        <v>804</v>
-      </c>
-      <c r="J1842">
-        <v>28</v>
-      </c>
-      <c r="K1842">
-        <v>49.3</v>
-      </c>
-    </row>
-    <row r="1843" spans="1:11">
-      <c r="A1843">
-        <v>296</v>
-      </c>
-      <c r="B1843">
-        <v>97</v>
-      </c>
-      <c r="C1843">
-        <v>0</v>
-      </c>
-      <c r="D1843">
-        <v>219</v>
-      </c>
-      <c r="E1843">
-        <v>0.557251908396947</v>
-      </c>
-      <c r="F1843">
-        <v>0.739864864864865</v>
-      </c>
-      <c r="G1843">
-        <v>0.0304054054054054</v>
-      </c>
-      <c r="H1843">
-        <v>932</v>
-      </c>
-      <c r="I1843">
-        <v>685</v>
-      </c>
-      <c r="J1843">
-        <v>28</v>
-      </c>
-      <c r="K1843">
-        <v>29.23</v>
-      </c>
-    </row>
-    <row r="1844" spans="1:11">
-      <c r="A1844">
-        <v>305</v>
-      </c>
-      <c r="B1844">
-        <v>100</v>
-      </c>
-      <c r="C1844">
-        <v>0</v>
-      </c>
-      <c r="D1844">
-        <v>196</v>
-      </c>
-      <c r="E1844">
-        <v>0.483950617283951</v>
-      </c>
-      <c r="F1844">
-        <v>0.642622950819672</v>
-      </c>
-      <c r="G1844">
-        <v>0.0327868852459016</v>
-      </c>
-      <c r="H1844">
-        <v>959</v>
-      </c>
-      <c r="I1844">
-        <v>705</v>
-      </c>
-      <c r="J1844">
-        <v>28</v>
-      </c>
-      <c r="K1844">
-        <v>29.77</v>
-      </c>
-    </row>
-    <row r="1845" spans="1:11">
-      <c r="A1845">
-        <v>310</v>
-      </c>
-      <c r="B1845">
-        <v>0</v>
-      </c>
-      <c r="C1845">
-        <v>143</v>
-      </c>
-      <c r="D1845">
-        <v>218</v>
-      </c>
-      <c r="E1845">
-        <v>0.481236203090508</v>
-      </c>
-      <c r="F1845">
-        <v>0.703225806451613</v>
-      </c>
-      <c r="G1845">
-        <v>0.032258064516129</v>
-      </c>
-      <c r="H1845">
-        <v>787</v>
-      </c>
-      <c r="I1845">
-        <v>804</v>
-      </c>
-      <c r="J1845">
-        <v>28</v>
-      </c>
-      <c r="K1845">
-        <v>36.19</v>
-      </c>
-    </row>
-    <row r="1846" spans="1:11">
-      <c r="A1846">
-        <v>148</v>
-      </c>
-      <c r="B1846">
-        <v>180</v>
-      </c>
-      <c r="C1846">
-        <v>0</v>
-      </c>
-      <c r="D1846">
-        <v>183</v>
-      </c>
-      <c r="E1846">
-        <v>0.557926829268293</v>
-      </c>
-      <c r="F1846">
-        <v>1.23648648648649</v>
-      </c>
-      <c r="G1846">
-        <v>0.0743243243243243</v>
-      </c>
-      <c r="H1846">
-        <v>972</v>
-      </c>
-      <c r="I1846">
-        <v>757</v>
-      </c>
-      <c r="J1846">
-        <v>28</v>
-      </c>
-      <c r="K1846">
-        <v>18.52</v>
-      </c>
-    </row>
-    <row r="1847" spans="1:11">
-      <c r="A1847">
-        <v>146</v>
-      </c>
-      <c r="B1847">
-        <v>178</v>
-      </c>
-      <c r="C1847">
-        <v>0</v>
-      </c>
-      <c r="D1847">
-        <v>192</v>
-      </c>
-      <c r="E1847">
-        <v>0.592592592592593</v>
-      </c>
-      <c r="F1847">
-        <v>1.31506849315069</v>
-      </c>
-      <c r="G1847">
-        <v>0.0753424657534247</v>
-      </c>
-      <c r="H1847">
-        <v>961</v>
-      </c>
-      <c r="I1847">
-        <v>749</v>
-      </c>
-      <c r="J1847">
-        <v>28</v>
-      </c>
-      <c r="K1847">
-        <v>17.19</v>
-      </c>
-    </row>
-    <row r="1848" spans="1:11">
-      <c r="A1848">
-        <v>142</v>
-      </c>
-      <c r="B1848">
-        <v>130</v>
-      </c>
-      <c r="C1848">
-        <v>167</v>
-      </c>
-      <c r="D1848">
-        <v>174</v>
-      </c>
-      <c r="E1848">
-        <v>0.396355353075171</v>
-      </c>
-      <c r="F1848">
-        <v>1.22535211267606</v>
-      </c>
-      <c r="G1848">
-        <v>0.0774647887323944</v>
-      </c>
-      <c r="H1848">
-        <v>883</v>
-      </c>
-      <c r="I1848">
-        <v>785</v>
-      </c>
-      <c r="J1848">
-        <v>28</v>
-      </c>
-      <c r="K1848">
-        <v>36.72</v>
-      </c>
-    </row>
-    <row r="1849" spans="1:11">
-      <c r="A1849">
-        <v>140</v>
-      </c>
-      <c r="B1849">
-        <v>128</v>
-      </c>
-      <c r="C1849">
-        <v>164</v>
-      </c>
-      <c r="D1849">
-        <v>183</v>
-      </c>
-      <c r="E1849">
-        <v>0.423611111111111</v>
-      </c>
-      <c r="F1849">
-        <v>1.30714285714286</v>
-      </c>
-      <c r="G1849">
-        <v>0.0857142857142857</v>
-      </c>
-      <c r="H1849">
-        <v>871</v>
-      </c>
-      <c r="I1849">
-        <v>775</v>
-      </c>
-      <c r="J1849">
-        <v>28</v>
-      </c>
-      <c r="K1849">
-        <v>33.38</v>
-      </c>
-    </row>
-    <row r="1850" spans="1:11">
-      <c r="A1850">
-        <v>308</v>
-      </c>
-      <c r="B1850">
-        <v>111</v>
-      </c>
-      <c r="C1850">
-        <v>142</v>
-      </c>
-      <c r="D1850">
-        <v>217</v>
-      </c>
-      <c r="E1850">
-        <v>0.38680926916221</v>
-      </c>
-      <c r="F1850">
-        <v>0.704545454545455</v>
-      </c>
-      <c r="G1850">
-        <v>0.0324675324675325</v>
-      </c>
-      <c r="H1850">
-        <v>783</v>
-      </c>
-      <c r="I1850">
-        <v>686</v>
-      </c>
-      <c r="J1850">
-        <v>28</v>
-      </c>
-      <c r="K1850">
-        <v>42.08</v>
-      </c>
-    </row>
-    <row r="1851" spans="1:11">
-      <c r="A1851">
-        <v>295</v>
-      </c>
-      <c r="B1851">
-        <v>106</v>
-      </c>
-      <c r="C1851">
-        <v>136</v>
-      </c>
-      <c r="D1851">
-        <v>208</v>
-      </c>
-      <c r="E1851">
-        <v>0.387337057728119</v>
-      </c>
-      <c r="F1851">
-        <v>0.705084745762712</v>
-      </c>
-      <c r="G1851">
-        <v>0.0203389830508475</v>
-      </c>
-      <c r="H1851">
-        <v>871</v>
-      </c>
-      <c r="I1851">
-        <v>650</v>
-      </c>
-      <c r="J1851">
-        <v>28</v>
-      </c>
-      <c r="K1851">
-        <v>39.4</v>
-      </c>
-    </row>
-    <row r="1852" spans="1:11">
-      <c r="A1852">
-        <v>298</v>
-      </c>
-      <c r="B1852">
-        <v>107</v>
-      </c>
-      <c r="C1852">
-        <v>137</v>
-      </c>
-      <c r="D1852">
-        <v>201</v>
-      </c>
-      <c r="E1852">
-        <v>0.370848708487085</v>
-      </c>
-      <c r="F1852">
-        <v>0.674496644295302</v>
-      </c>
-      <c r="G1852">
-        <v>0.0201342281879195</v>
-      </c>
-      <c r="H1852">
-        <v>878</v>
-      </c>
-      <c r="I1852">
-        <v>655</v>
-      </c>
-      <c r="J1852">
-        <v>28</v>
-      </c>
-      <c r="K1852">
-        <v>41.27</v>
-      </c>
-    </row>
-    <row r="1853" spans="1:11">
-      <c r="A1853">
-        <v>314</v>
-      </c>
-      <c r="B1853">
-        <v>0</v>
-      </c>
-      <c r="C1853">
-        <v>161</v>
-      </c>
-      <c r="D1853">
-        <v>207</v>
-      </c>
-      <c r="E1853">
-        <v>0.435789473684211</v>
-      </c>
-      <c r="F1853">
-        <v>0.659235668789809</v>
-      </c>
-      <c r="G1853">
-        <v>0.0191082802547771</v>
-      </c>
-      <c r="H1853">
-        <v>851</v>
-      </c>
-      <c r="I1853">
-        <v>757</v>
-      </c>
-      <c r="J1853">
-        <v>28</v>
-      </c>
-      <c r="K1853">
-        <v>41.14</v>
-      </c>
-    </row>
-    <row r="1854" spans="1:11">
-      <c r="A1854">
-        <v>321</v>
-      </c>
-      <c r="B1854">
-        <v>0</v>
-      </c>
-      <c r="C1854">
-        <v>164</v>
-      </c>
-      <c r="D1854">
-        <v>190</v>
-      </c>
-      <c r="E1854">
-        <v>0.391752577319588</v>
-      </c>
-      <c r="F1854">
-        <v>0.59190031152648</v>
-      </c>
-      <c r="G1854">
-        <v>0.0155763239875389</v>
-      </c>
-      <c r="H1854">
-        <v>870</v>
-      </c>
-      <c r="I1854">
-        <v>774</v>
-      </c>
-      <c r="J1854">
-        <v>28</v>
-      </c>
-      <c r="K1854">
-        <v>45.82</v>
-      </c>
-    </row>
-    <row r="1855" spans="1:11">
-      <c r="A1855">
-        <v>349</v>
-      </c>
-      <c r="B1855">
-        <v>0</v>
-      </c>
-      <c r="C1855">
-        <v>178</v>
-      </c>
-      <c r="D1855">
-        <v>230</v>
-      </c>
-      <c r="E1855">
-        <v>0.436432637571158</v>
-      </c>
-      <c r="F1855">
-        <v>0.659025787965616</v>
-      </c>
-      <c r="G1855">
-        <v>0.0171919770773639</v>
-      </c>
-      <c r="H1855">
-        <v>785</v>
-      </c>
-      <c r="I1855">
-        <v>721</v>
-      </c>
-      <c r="J1855">
-        <v>28</v>
-      </c>
-      <c r="K1855">
-        <v>43.95</v>
-      </c>
-    </row>
-    <row r="1856" spans="1:11">
-      <c r="A1856">
-        <v>366</v>
-      </c>
-      <c r="B1856">
-        <v>0</v>
-      </c>
-      <c r="C1856">
-        <v>187</v>
-      </c>
-      <c r="D1856">
-        <v>191</v>
-      </c>
-      <c r="E1856">
-        <v>0.345388788426763</v>
-      </c>
-      <c r="F1856">
-        <v>0.521857923497268</v>
-      </c>
-      <c r="G1856">
-        <v>0.0191256830601093</v>
-      </c>
-      <c r="H1856">
-        <v>824</v>
-      </c>
-      <c r="I1856">
-        <v>757</v>
-      </c>
-      <c r="J1856">
-        <v>28</v>
-      </c>
-      <c r="K1856">
-        <v>52.65</v>
-      </c>
-    </row>
-    <row r="1857" spans="1:11">
-      <c r="A1857">
-        <v>274</v>
-      </c>
-      <c r="B1857">
-        <v>89</v>
-      </c>
-      <c r="C1857">
-        <v>115</v>
-      </c>
-      <c r="D1857">
-        <v>202</v>
-      </c>
-      <c r="E1857">
-        <v>0.422594142259414</v>
-      </c>
-      <c r="F1857">
-        <v>0.737226277372263</v>
-      </c>
-      <c r="G1857">
-        <v>0.0328467153284671</v>
-      </c>
-      <c r="H1857">
-        <v>759</v>
-      </c>
-      <c r="I1857">
-        <v>827</v>
-      </c>
-      <c r="J1857">
-        <v>28</v>
-      </c>
-      <c r="K1857">
-        <v>35.52</v>
-      </c>
-    </row>
-    <row r="1858" spans="1:11">
-      <c r="A1858">
-        <v>137</v>
-      </c>
-      <c r="B1858">
-        <v>167</v>
-      </c>
-      <c r="C1858">
-        <v>214</v>
-      </c>
-      <c r="D1858">
-        <v>226</v>
-      </c>
-      <c r="E1858">
-        <v>0.436293436293436</v>
-      </c>
-      <c r="F1858">
-        <v>1.64963503649635</v>
-      </c>
-      <c r="G1858">
-        <v>0.0437956204379562</v>
-      </c>
-      <c r="H1858">
-        <v>708</v>
-      </c>
-      <c r="I1858">
-        <v>757</v>
-      </c>
-      <c r="J1858">
-        <v>28</v>
-      </c>
-      <c r="K1858">
-        <v>34.45</v>
-      </c>
-    </row>
-    <row r="1859" spans="1:11">
-      <c r="A1859">
-        <v>275</v>
-      </c>
-      <c r="B1859">
-        <v>99</v>
-      </c>
-      <c r="C1859">
-        <v>127</v>
-      </c>
-      <c r="D1859">
-        <v>184</v>
-      </c>
-      <c r="E1859">
-        <v>0.367265469061876</v>
-      </c>
-      <c r="F1859">
-        <v>0.669090909090909</v>
-      </c>
-      <c r="G1859">
-        <v>0.0472727272727273</v>
-      </c>
-      <c r="H1859">
-        <v>810</v>
-      </c>
-      <c r="I1859">
-        <v>790</v>
-      </c>
-      <c r="J1859">
-        <v>28</v>
-      </c>
-      <c r="K1859">
-        <v>43.54</v>
-      </c>
-    </row>
-    <row r="1860" spans="1:11">
-      <c r="A1860">
-        <v>252</v>
-      </c>
-      <c r="B1860">
-        <v>76</v>
-      </c>
-      <c r="C1860">
-        <v>97</v>
-      </c>
-      <c r="D1860">
-        <v>194</v>
-      </c>
-      <c r="E1860">
-        <v>0.456470588235294</v>
-      </c>
-      <c r="F1860">
-        <v>0.76984126984127</v>
-      </c>
-      <c r="G1860">
-        <v>0.0317460317460317</v>
-      </c>
-      <c r="H1860">
-        <v>835</v>
-      </c>
-      <c r="I1860">
-        <v>821</v>
-      </c>
-      <c r="J1860">
-        <v>28</v>
-      </c>
-      <c r="K1860">
-        <v>33.11</v>
-      </c>
-    </row>
-    <row r="1861" spans="1:11">
-      <c r="A1861">
-        <v>165</v>
-      </c>
-      <c r="B1861">
-        <v>150</v>
-      </c>
-      <c r="C1861">
-        <v>0</v>
-      </c>
-      <c r="D1861">
-        <v>182</v>
-      </c>
-      <c r="E1861">
-        <v>0.577777777777778</v>
-      </c>
-      <c r="F1861">
-        <v>1.1030303030303</v>
-      </c>
-      <c r="G1861">
-        <v>0.0727272727272727</v>
-      </c>
-      <c r="H1861">
-        <v>1023</v>
-      </c>
-      <c r="I1861">
-        <v>729</v>
-      </c>
-      <c r="J1861">
-        <v>28</v>
-      </c>
-      <c r="K1861">
-        <v>18.26</v>
-      </c>
-    </row>
-    <row r="1862" spans="1:11">
-      <c r="A1862">
-        <v>158</v>
-      </c>
-      <c r="B1862">
-        <v>0</v>
-      </c>
-      <c r="C1862">
-        <v>246</v>
-      </c>
-      <c r="D1862">
-        <v>174</v>
-      </c>
-      <c r="E1862">
-        <v>0.430693069306931</v>
-      </c>
-      <c r="F1862">
-        <v>1.10126582278481</v>
-      </c>
-      <c r="G1862">
-        <v>0.0443037974683544</v>
-      </c>
-      <c r="H1862">
-        <v>1035</v>
-      </c>
-      <c r="I1862">
-        <v>706</v>
-      </c>
-      <c r="J1862">
-        <v>28</v>
-      </c>
-      <c r="K1862">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="1863" spans="1:11">
-      <c r="A1863">
-        <v>156</v>
-      </c>
-      <c r="B1863">
-        <v>0</v>
-      </c>
-      <c r="C1863">
-        <v>243</v>
-      </c>
-      <c r="D1863">
-        <v>180</v>
-      </c>
-      <c r="E1863">
-        <v>0.451127819548872</v>
-      </c>
-      <c r="F1863">
-        <v>1.15384615384615</v>
-      </c>
-      <c r="G1863">
-        <v>0.0705128205128205</v>
-      </c>
-      <c r="H1863">
-        <v>1022</v>
-      </c>
-      <c r="I1863">
-        <v>698</v>
-      </c>
-      <c r="J1863">
-        <v>28</v>
-      </c>
-      <c r="K1863">
-        <v>33.78</v>
-      </c>
-    </row>
-    <row r="1864" spans="1:11">
-      <c r="A1864">
-        <v>145</v>
-      </c>
-      <c r="B1864">
-        <v>177</v>
-      </c>
-      <c r="C1864">
-        <v>227</v>
-      </c>
-      <c r="D1864">
-        <v>209</v>
-      </c>
-      <c r="E1864">
-        <v>0.380692167577413</v>
-      </c>
-      <c r="F1864">
-        <v>1.44137931034483</v>
-      </c>
-      <c r="G1864">
-        <v>0.0758620689655172</v>
-      </c>
-      <c r="H1864">
-        <v>752</v>
-      </c>
-      <c r="I1864">
-        <v>715</v>
-      </c>
-      <c r="J1864">
-        <v>28</v>
-      </c>
-      <c r="K1864">
-        <v>35.66</v>
-      </c>
-    </row>
-    <row r="1865" spans="1:11">
-      <c r="A1865">
-        <v>154</v>
-      </c>
-      <c r="B1865">
-        <v>141</v>
-      </c>
-      <c r="C1865">
-        <v>181</v>
-      </c>
-      <c r="D1865">
-        <v>234</v>
-      </c>
-      <c r="E1865">
-        <v>0.491596638655462</v>
-      </c>
-      <c r="F1865">
-        <v>1.51948051948052</v>
-      </c>
-      <c r="G1865">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="H1865">
-        <v>797</v>
-      </c>
-      <c r="I1865">
-        <v>683</v>
-      </c>
-      <c r="J1865">
-        <v>28</v>
-      </c>
-      <c r="K1865">
-        <v>33.51</v>
-      </c>
-    </row>
-    <row r="1866" spans="1:11">
-      <c r="A1866">
-        <v>160</v>
-      </c>
-      <c r="B1866">
-        <v>146</v>
-      </c>
-      <c r="C1866">
-        <v>188</v>
-      </c>
-      <c r="D1866">
-        <v>203</v>
-      </c>
-      <c r="E1866">
-        <v>0.410931174089069</v>
-      </c>
-      <c r="F1866">
-        <v>1.26875</v>
-      </c>
-      <c r="G1866">
-        <v>0.06875</v>
-      </c>
-      <c r="H1866">
-        <v>829</v>
-      </c>
-      <c r="I1866">
-        <v>710</v>
-      </c>
-      <c r="J1866">
-        <v>28</v>
-      </c>
-      <c r="K1866">
-        <v>33.51</v>
-      </c>
-    </row>
-    <row r="1867" spans="1:11">
-      <c r="A1867">
-        <v>291</v>
-      </c>
-      <c r="B1867">
-        <v>105</v>
-      </c>
-      <c r="C1867">
-        <v>0</v>
-      </c>
-      <c r="D1867">
-        <v>205</v>
-      </c>
-      <c r="E1867">
-        <v>0.517676767676768</v>
-      </c>
-      <c r="F1867">
-        <v>0.70446735395189</v>
-      </c>
-      <c r="G1867">
-        <v>0.0206185567010309</v>
-      </c>
-      <c r="H1867">
-        <v>859</v>
-      </c>
-      <c r="I1867">
-        <v>797</v>
-      </c>
-      <c r="J1867">
-        <v>28</v>
-      </c>
-      <c r="K1867">
-        <v>27.62</v>
-      </c>
-    </row>
-    <row r="1868" spans="1:11">
-      <c r="A1868">
-        <v>298</v>
-      </c>
-      <c r="B1868">
-        <v>107</v>
-      </c>
-      <c r="C1868">
-        <v>0</v>
-      </c>
-      <c r="D1868">
-        <v>186</v>
-      </c>
-      <c r="E1868">
-        <v>0.459259259259259</v>
-      </c>
-      <c r="F1868">
-        <v>0.624161073825503</v>
-      </c>
-      <c r="G1868">
-        <v>0.0201342281879195</v>
-      </c>
-      <c r="H1868">
-        <v>879</v>
-      </c>
-      <c r="I1868">
-        <v>815</v>
-      </c>
-      <c r="J1868">
-        <v>28</v>
-      </c>
-      <c r="K1868">
-        <v>30.97</v>
-      </c>
-    </row>
-    <row r="1869" spans="1:11">
-      <c r="A1869">
-        <v>318</v>
-      </c>
-      <c r="B1869">
-        <v>126</v>
-      </c>
-      <c r="C1869">
-        <v>0</v>
-      </c>
-      <c r="D1869">
-        <v>210</v>
-      </c>
-      <c r="E1869">
-        <v>0.472972972972973</v>
-      </c>
-      <c r="F1869">
-        <v>0.660377358490566</v>
-      </c>
-      <c r="G1869">
-        <v>0.0188679245283019</v>
-      </c>
-      <c r="H1869">
-        <v>861</v>
-      </c>
-      <c r="I1869">
-        <v>737</v>
-      </c>
-      <c r="J1869">
-        <v>28</v>
-      </c>
-      <c r="K1869">
-        <v>31.77</v>
-      </c>
-    </row>
-    <row r="1870" spans="1:11">
-      <c r="A1870">
-        <v>280</v>
-      </c>
-      <c r="B1870">
-        <v>92</v>
-      </c>
-      <c r="C1870">
-        <v>118</v>
-      </c>
-      <c r="D1870">
-        <v>207</v>
-      </c>
-      <c r="E1870">
-        <v>0.422448979591837</v>
-      </c>
-      <c r="F1870">
-        <v>0.739285714285714</v>
-      </c>
-      <c r="G1870">
-        <v>0.0321428571428571</v>
-      </c>
-      <c r="H1870">
-        <v>883</v>
-      </c>
-      <c r="I1870">
-        <v>679</v>
-      </c>
-      <c r="J1870">
-        <v>28</v>
-      </c>
-      <c r="K1870">
-        <v>37.39</v>
-      </c>
-    </row>
-    <row r="1871" spans="1:11">
-      <c r="A1871">
-        <v>287</v>
-      </c>
-      <c r="B1871">
-        <v>94</v>
-      </c>
-      <c r="C1871">
-        <v>121</v>
-      </c>
-      <c r="D1871">
-        <v>188</v>
-      </c>
-      <c r="E1871">
-        <v>0.374501992031873</v>
-      </c>
-      <c r="F1871">
-        <v>0.655052264808362</v>
-      </c>
-      <c r="G1871">
-        <v>0.0313588850174216</v>
-      </c>
-      <c r="H1871">
-        <v>904</v>
-      </c>
-      <c r="I1871">
-        <v>696</v>
-      </c>
-      <c r="J1871">
-        <v>28</v>
-      </c>
-      <c r="K1871">
-        <v>43.01</v>
-      </c>
-    </row>
-    <row r="1872" spans="1:11">
-      <c r="A1872">
-        <v>332</v>
-      </c>
-      <c r="B1872">
-        <v>0</v>
-      </c>
-      <c r="C1872">
-        <v>170</v>
-      </c>
-      <c r="D1872">
-        <v>160</v>
-      </c>
-      <c r="E1872">
-        <v>0.318725099601594</v>
-      </c>
-      <c r="F1872">
-        <v>0.481927710843373</v>
-      </c>
-      <c r="G1872">
-        <v>0.0180722891566265</v>
-      </c>
-      <c r="H1872">
-        <v>900</v>
-      </c>
-      <c r="I1872">
-        <v>806</v>
-      </c>
-      <c r="J1872">
-        <v>28</v>
-      </c>
-      <c r="K1872">
-        <v>58.53</v>
-      </c>
-    </row>
-    <row r="1873" spans="1:11">
-      <c r="A1873">
-        <v>326</v>
-      </c>
-      <c r="B1873">
-        <v>0</v>
-      </c>
-      <c r="C1873">
-        <v>167</v>
-      </c>
-      <c r="D1873">
-        <v>174</v>
-      </c>
-      <c r="E1873">
-        <v>0.352941176470588</v>
-      </c>
-      <c r="F1873">
-        <v>0.533742331288344</v>
-      </c>
-      <c r="G1873">
-        <v>0.0184049079754601</v>
-      </c>
-      <c r="H1873">
-        <v>884</v>
-      </c>
-      <c r="I1873">
-        <v>792</v>
-      </c>
-      <c r="J1873">
-        <v>28</v>
-      </c>
-      <c r="K1873">
-        <v>52.65</v>
-      </c>
-    </row>
-    <row r="1874" spans="1:11">
-      <c r="A1874">
-        <v>320</v>
-      </c>
-      <c r="B1874">
-        <v>0</v>
-      </c>
-      <c r="C1874">
-        <v>163</v>
-      </c>
-      <c r="D1874">
-        <v>188</v>
-      </c>
-      <c r="E1874">
-        <v>0.389233954451346</v>
-      </c>
-      <c r="F1874">
-        <v>0.5875</v>
-      </c>
-      <c r="G1874">
-        <v>0.028125</v>
-      </c>
-      <c r="H1874">
-        <v>866</v>
-      </c>
-      <c r="I1874">
-        <v>776</v>
-      </c>
-      <c r="J1874">
-        <v>28</v>
-      </c>
-      <c r="K1874">
-        <v>45.69</v>
-      </c>
-    </row>
-    <row r="1875" spans="1:11">
-      <c r="A1875">
-        <v>342</v>
-      </c>
-      <c r="B1875">
-        <v>136</v>
-      </c>
-      <c r="C1875">
-        <v>0</v>
-      </c>
-      <c r="D1875">
-        <v>225</v>
-      </c>
-      <c r="E1875">
-        <v>0.47071129707113</v>
-      </c>
-      <c r="F1875">
-        <v>0.657894736842105</v>
-      </c>
-      <c r="G1875">
-        <v>0.0321637426900585</v>
-      </c>
-      <c r="H1875">
-        <v>770</v>
-      </c>
-      <c r="I1875">
-        <v>747</v>
-      </c>
-      <c r="J1875">
-        <v>28</v>
-      </c>
-      <c r="K1875">
-        <v>32.04</v>
-      </c>
-    </row>
-    <row r="1876" spans="1:11">
-      <c r="A1876">
-        <v>356</v>
-      </c>
-      <c r="B1876">
-        <v>142</v>
-      </c>
-      <c r="C1876">
-        <v>0</v>
-      </c>
-      <c r="D1876">
-        <v>193</v>
-      </c>
-      <c r="E1876">
-        <v>0.387550200803213</v>
-      </c>
-      <c r="F1876">
-        <v>0.542134831460674</v>
-      </c>
-      <c r="G1876">
-        <v>0.0308988764044944</v>
-      </c>
-      <c r="H1876">
-        <v>801</v>
-      </c>
-      <c r="I1876">
-        <v>778</v>
-      </c>
-      <c r="J1876">
-        <v>28</v>
-      </c>
-      <c r="K1876">
-        <v>36.46</v>
-      </c>
-    </row>
-    <row r="1877" spans="1:11">
-      <c r="A1877">
-        <v>309</v>
-      </c>
-      <c r="B1877">
-        <v>0</v>
-      </c>
-      <c r="C1877">
-        <v>142</v>
-      </c>
-      <c r="D1877">
-        <v>218</v>
-      </c>
-      <c r="E1877">
-        <v>0.483370288248337</v>
-      </c>
-      <c r="F1877">
-        <v>0.705501618122977</v>
-      </c>
-      <c r="G1877">
-        <v>0.0323624595469256</v>
-      </c>
-      <c r="H1877">
-        <v>912</v>
-      </c>
-      <c r="I1877">
-        <v>680</v>
-      </c>
-      <c r="J1877">
-        <v>28</v>
-      </c>
-      <c r="K1877">
-        <v>38.59</v>
-      </c>
-    </row>
-    <row r="1878" spans="1:11">
-      <c r="A1878">
-        <v>322</v>
-      </c>
-      <c r="B1878">
-        <v>0</v>
-      </c>
-      <c r="C1878">
-        <v>149</v>
-      </c>
-      <c r="D1878">
-        <v>186</v>
-      </c>
-      <c r="E1878">
-        <v>0.394904458598726</v>
-      </c>
-      <c r="F1878">
-        <v>0.577639751552795</v>
-      </c>
-      <c r="G1878">
-        <v>0.0248447204968944</v>
-      </c>
-      <c r="H1878">
-        <v>951</v>
-      </c>
-      <c r="I1878">
-        <v>709</v>
-      </c>
-      <c r="J1878">
-        <v>28</v>
-      </c>
-      <c r="K1878">
-        <v>45.42</v>
-      </c>
-    </row>
-    <row r="1879" spans="1:11">
-      <c r="A1879">
-        <v>159</v>
-      </c>
-      <c r="B1879">
-        <v>193</v>
-      </c>
-      <c r="C1879">
-        <v>0</v>
-      </c>
-      <c r="D1879">
-        <v>208</v>
-      </c>
-      <c r="E1879">
-        <v>0.590909090909091</v>
-      </c>
-      <c r="F1879">
-        <v>1.30817610062893</v>
-      </c>
-      <c r="G1879">
-        <v>0.0754716981132075</v>
-      </c>
-      <c r="H1879">
-        <v>821</v>
-      </c>
-      <c r="I1879">
-        <v>818</v>
-      </c>
-      <c r="J1879">
-        <v>28</v>
-      </c>
-      <c r="K1879">
-        <v>19.19</v>
-      </c>
-    </row>
-    <row r="1880" spans="1:11">
-      <c r="A1880">
-        <v>307</v>
-      </c>
-      <c r="B1880">
-        <v>110</v>
-      </c>
-      <c r="C1880">
-        <v>0</v>
-      </c>
-      <c r="D1880">
-        <v>189</v>
-      </c>
-      <c r="E1880">
-        <v>0.453237410071943</v>
-      </c>
-      <c r="F1880">
-        <v>0.615635179153095</v>
-      </c>
-      <c r="G1880">
-        <v>0.0325732899022801</v>
-      </c>
-      <c r="H1880">
-        <v>904</v>
-      </c>
-      <c r="I1880">
-        <v>765</v>
-      </c>
-      <c r="J1880">
-        <v>28</v>
-      </c>
-      <c r="K1880">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="1881" spans="1:11">
-      <c r="A1881">
-        <v>313</v>
-      </c>
-      <c r="B1881">
-        <v>124</v>
-      </c>
-      <c r="C1881">
-        <v>0</v>
-      </c>
-      <c r="D1881">
-        <v>205</v>
-      </c>
-      <c r="E1881">
-        <v>0.469107551487414</v>
-      </c>
-      <c r="F1881">
-        <v>0.654952076677316</v>
-      </c>
-      <c r="G1881">
-        <v>0.0351437699680511</v>
-      </c>
-      <c r="H1881">
-        <v>846</v>
-      </c>
-      <c r="I1881">
-        <v>758</v>
-      </c>
-      <c r="J1881">
-        <v>28</v>
-      </c>
-      <c r="K1881">
-        <v>29.63</v>
-      </c>
-    </row>
-    <row r="1882" spans="1:11">
-      <c r="A1882">
-        <v>143</v>
-      </c>
-      <c r="B1882">
-        <v>131</v>
-      </c>
-      <c r="C1882">
-        <v>168</v>
-      </c>
-      <c r="D1882">
-        <v>217</v>
-      </c>
-      <c r="E1882">
-        <v>0.490950226244344</v>
-      </c>
-      <c r="F1882">
-        <v>1.51748251748252</v>
-      </c>
-      <c r="G1882">
-        <v>0.041958041958042</v>
-      </c>
-      <c r="H1882">
-        <v>891</v>
-      </c>
-      <c r="I1882">
-        <v>672</v>
-      </c>
-      <c r="J1882">
-        <v>28</v>
-      </c>
-      <c r="K1882">
-        <v>26.42</v>
-      </c>
-    </row>
-    <row r="1883" spans="1:11">
-      <c r="A1883">
-        <v>140</v>
-      </c>
-      <c r="B1883">
-        <v>128</v>
-      </c>
-      <c r="C1883">
-        <v>164</v>
-      </c>
-      <c r="D1883">
-        <v>237</v>
-      </c>
-      <c r="E1883">
-        <v>0.548611111111111</v>
-      </c>
-      <c r="F1883">
-        <v>1.69285714285714</v>
-      </c>
-      <c r="G1883">
-        <v>0.0428571428571429</v>
-      </c>
-      <c r="H1883">
-        <v>869</v>
-      </c>
-      <c r="I1883">
-        <v>656</v>
-      </c>
-      <c r="J1883">
-        <v>28</v>
-      </c>
-      <c r="K1883">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="1884" spans="1:11">
-      <c r="A1884">
-        <v>278</v>
-      </c>
-      <c r="B1884">
-        <v>0</v>
-      </c>
-      <c r="C1884">
-        <v>117</v>
-      </c>
-      <c r="D1884">
-        <v>205</v>
-      </c>
-      <c r="E1884">
-        <v>0.518987341772152</v>
-      </c>
-      <c r="F1884">
-        <v>0.737410071942446</v>
-      </c>
-      <c r="G1884">
-        <v>0.0323741007194245</v>
-      </c>
-      <c r="H1884">
-        <v>875</v>
-      </c>
-      <c r="I1884">
-        <v>799</v>
-      </c>
-      <c r="J1884">
-        <v>28</v>
-      </c>
-      <c r="K1884">
-        <v>32.71</v>
-      </c>
-    </row>
-    <row r="1885" spans="1:11">
-      <c r="A1885">
-        <v>288</v>
-      </c>
-      <c r="B1885">
-        <v>0</v>
-      </c>
-      <c r="C1885">
-        <v>121</v>
-      </c>
-      <c r="D1885">
-        <v>177</v>
-      </c>
-      <c r="E1885">
-        <v>0.432762836185819</v>
-      </c>
-      <c r="F1885">
-        <v>0.614583333333333</v>
-      </c>
-      <c r="G1885">
-        <v>0.0243055555555556</v>
-      </c>
-      <c r="H1885">
-        <v>908</v>
-      </c>
-      <c r="I1885">
-        <v>829</v>
-      </c>
-      <c r="J1885">
-        <v>28</v>
-      </c>
-      <c r="K1885">
-        <v>39.93</v>
-      </c>
-    </row>
-    <row r="1886" spans="1:11">
-      <c r="A1886">
-        <v>299</v>
-      </c>
-      <c r="B1886">
-        <v>107</v>
-      </c>
-      <c r="C1886">
-        <v>0</v>
-      </c>
-      <c r="D1886">
-        <v>210</v>
-      </c>
-      <c r="E1886">
-        <v>0.517241379310345</v>
-      </c>
-      <c r="F1886">
-        <v>0.702341137123746</v>
-      </c>
-      <c r="G1886">
-        <v>0.0334448160535117</v>
-      </c>
-      <c r="H1886">
-        <v>881</v>
-      </c>
-      <c r="I1886">
-        <v>745</v>
-      </c>
-      <c r="J1886">
-        <v>28</v>
-      </c>
-      <c r="K1886">
-        <v>28.29</v>
-      </c>
-    </row>
-    <row r="1887" spans="1:11">
-      <c r="A1887">
-        <v>291</v>
-      </c>
-      <c r="B1887">
-        <v>104</v>
-      </c>
-      <c r="C1887">
-        <v>0</v>
-      </c>
-      <c r="D1887">
-        <v>231</v>
-      </c>
-      <c r="E1887">
-        <v>0.584810126582278</v>
-      </c>
-      <c r="F1887">
-        <v>0.793814432989691</v>
-      </c>
-      <c r="G1887">
-        <v>0.0309278350515464</v>
-      </c>
-      <c r="H1887">
-        <v>857</v>
-      </c>
-      <c r="I1887">
-        <v>725</v>
-      </c>
-      <c r="J1887">
-        <v>28</v>
-      </c>
-      <c r="K1887">
-        <v>30.43</v>
-      </c>
-    </row>
-    <row r="1888" spans="1:11">
-      <c r="A1888">
-        <v>265</v>
-      </c>
-      <c r="B1888">
-        <v>86</v>
-      </c>
-      <c r="C1888">
-        <v>111</v>
-      </c>
-      <c r="D1888">
-        <v>195</v>
-      </c>
-      <c r="E1888">
-        <v>0.422077922077922</v>
-      </c>
-      <c r="F1888">
-        <v>0.735849056603774</v>
-      </c>
-      <c r="G1888">
-        <v>0.0226415094339623</v>
-      </c>
-      <c r="H1888">
-        <v>833</v>
-      </c>
-      <c r="I1888">
-        <v>790</v>
-      </c>
-      <c r="J1888">
-        <v>28</v>
-      </c>
-      <c r="K1888">
-        <v>37.39</v>
-      </c>
-    </row>
-    <row r="1889" spans="1:11">
-      <c r="A1889">
-        <v>159</v>
-      </c>
-      <c r="B1889">
-        <v>0</v>
-      </c>
-      <c r="C1889">
-        <v>248</v>
-      </c>
-      <c r="D1889">
-        <v>175</v>
-      </c>
-      <c r="E1889">
-        <v>0.42997542997543</v>
-      </c>
-      <c r="F1889">
-        <v>1.10062893081761</v>
-      </c>
-      <c r="G1889">
-        <v>0.0754716981132075</v>
-      </c>
-      <c r="H1889">
-        <v>1041</v>
-      </c>
-      <c r="I1889">
-        <v>683</v>
-      </c>
-      <c r="J1889">
-        <v>28</v>
-      </c>
-      <c r="K1889">
-        <v>35.39</v>
-      </c>
-    </row>
-    <row r="1890" spans="1:11">
-      <c r="A1890">
-        <v>160</v>
-      </c>
-      <c r="B1890">
-        <v>0</v>
-      </c>
-      <c r="C1890">
-        <v>250</v>
-      </c>
-      <c r="D1890">
-        <v>168</v>
-      </c>
-      <c r="E1890">
-        <v>0.409756097560976</v>
-      </c>
-      <c r="F1890">
-        <v>1.05</v>
-      </c>
-      <c r="G1890">
-        <v>0.075</v>
-      </c>
-      <c r="H1890">
-        <v>1049</v>
-      </c>
-      <c r="I1890">
-        <v>688</v>
-      </c>
-      <c r="J1890">
-        <v>28</v>
-      </c>
-      <c r="K1890">
-        <v>37.66</v>
-      </c>
-    </row>
-    <row r="1891" spans="1:11">
-      <c r="A1891">
-        <v>166</v>
-      </c>
-      <c r="B1891">
-        <v>0</v>
-      </c>
-      <c r="C1891">
-        <v>260</v>
-      </c>
-      <c r="D1891">
-        <v>183</v>
-      </c>
-      <c r="E1891">
-        <v>0.429577464788732</v>
-      </c>
-      <c r="F1891">
-        <v>1.10240963855422</v>
-      </c>
-      <c r="G1891">
-        <v>0.0783132530120482</v>
-      </c>
-      <c r="H1891">
-        <v>859</v>
-      </c>
-      <c r="I1891">
-        <v>827</v>
-      </c>
-      <c r="J1891">
-        <v>28</v>
-      </c>
-      <c r="K1891">
-        <v>40.34</v>
-      </c>
-    </row>
-    <row r="1892" spans="1:11">
-      <c r="A1892">
-        <v>320</v>
-      </c>
-      <c r="B1892">
-        <v>127</v>
-      </c>
-      <c r="C1892">
-        <v>164</v>
-      </c>
-      <c r="D1892">
-        <v>211</v>
-      </c>
-      <c r="E1892">
-        <v>0.345335515548282</v>
-      </c>
-      <c r="F1892">
-        <v>0.659375</v>
-      </c>
-      <c r="G1892">
-        <v>0.01875</v>
-      </c>
-      <c r="H1892">
-        <v>721</v>
-      </c>
-      <c r="I1892">
-        <v>723</v>
-      </c>
-      <c r="J1892">
-        <v>28</v>
-      </c>
-      <c r="K1892">
-        <v>46.36</v>
-      </c>
-    </row>
-    <row r="1893" spans="1:11">
-      <c r="A1893">
-        <v>336</v>
-      </c>
-      <c r="B1893">
-        <v>134</v>
-      </c>
-      <c r="C1893">
-        <v>0</v>
-      </c>
-      <c r="D1893">
-        <v>222</v>
-      </c>
-      <c r="E1893">
-        <v>0.472340425531915</v>
-      </c>
-      <c r="F1893">
-        <v>0.660714285714286</v>
-      </c>
-      <c r="G1893">
-        <v>0.0178571428571429</v>
-      </c>
-      <c r="H1893">
-        <v>756</v>
-      </c>
-      <c r="I1893">
-        <v>787</v>
-      </c>
-      <c r="J1893">
-        <v>28</v>
-      </c>
-      <c r="K1893">
-        <v>31.9</v>
-      </c>
-    </row>
-    <row r="1894" spans="1:11">
-      <c r="A1894">
-        <v>276</v>
-      </c>
-      <c r="B1894">
-        <v>90</v>
-      </c>
-      <c r="C1894">
-        <v>116</v>
-      </c>
-      <c r="D1894">
-        <v>180</v>
-      </c>
-      <c r="E1894">
-        <v>0.37344398340249</v>
-      </c>
-      <c r="F1894">
-        <v>0.652173913043478</v>
-      </c>
-      <c r="G1894">
-        <v>0.0326086956521739</v>
-      </c>
-      <c r="H1894">
-        <v>870</v>
-      </c>
-      <c r="I1894">
-        <v>768</v>
-      </c>
-      <c r="J1894">
-        <v>28</v>
-      </c>
-      <c r="K1894">
-        <v>44.08</v>
-      </c>
-    </row>
-    <row r="1895" spans="1:11">
-      <c r="A1895">
-        <v>313</v>
-      </c>
-      <c r="B1895">
-        <v>112</v>
-      </c>
-      <c r="C1895">
-        <v>0</v>
-      </c>
-      <c r="D1895">
-        <v>220</v>
-      </c>
-      <c r="E1895">
-        <v>0.517647058823529</v>
-      </c>
-      <c r="F1895">
-        <v>0.702875399361022</v>
-      </c>
-      <c r="G1895">
-        <v>0.0319488817891374</v>
-      </c>
-      <c r="H1895">
-        <v>794</v>
-      </c>
-      <c r="I1895">
-        <v>789</v>
-      </c>
-      <c r="J1895">
-        <v>28</v>
-      </c>
-      <c r="K1895">
-        <v>28.16</v>
-      </c>
-    </row>
-    <row r="1896" spans="1:11">
-      <c r="A1896">
-        <v>322</v>
-      </c>
-      <c r="B1896">
-        <v>116</v>
-      </c>
-      <c r="C1896">
-        <v>0</v>
-      </c>
-      <c r="D1896">
-        <v>196</v>
-      </c>
-      <c r="E1896">
-        <v>0.447488584474886</v>
-      </c>
-      <c r="F1896">
-        <v>0.608695652173913</v>
-      </c>
-      <c r="G1896">
-        <v>0.031055900621118</v>
-      </c>
-      <c r="H1896">
-        <v>818</v>
-      </c>
-      <c r="I1896">
-        <v>813</v>
-      </c>
-      <c r="J1896">
-        <v>28</v>
-      </c>
-      <c r="K1896">
-        <v>29.77</v>
-      </c>
-    </row>
-    <row r="1897" spans="1:11">
-      <c r="A1897">
-        <v>294</v>
-      </c>
-      <c r="B1897">
-        <v>106</v>
-      </c>
-      <c r="C1897">
-        <v>136</v>
-      </c>
-      <c r="D1897">
-        <v>207</v>
-      </c>
-      <c r="E1897">
-        <v>0.386194029850746</v>
-      </c>
-      <c r="F1897">
-        <v>0.704081632653061</v>
-      </c>
-      <c r="G1897">
-        <v>0.0204081632653061</v>
-      </c>
-      <c r="H1897">
-        <v>747</v>
-      </c>
-      <c r="I1897">
-        <v>778</v>
-      </c>
-      <c r="J1897">
-        <v>28</v>
-      </c>
-      <c r="K1897">
-        <v>41.27</v>
-      </c>
-    </row>
-    <row r="1898" spans="1:11">
-      <c r="A1898">
-        <v>146</v>
-      </c>
-      <c r="B1898">
-        <v>106</v>
-      </c>
-      <c r="C1898">
-        <v>137</v>
-      </c>
-      <c r="D1898">
-        <v>209</v>
-      </c>
-      <c r="E1898">
-        <v>0.537275064267352</v>
-      </c>
-      <c r="F1898">
-        <v>1.43150684931507</v>
-      </c>
-      <c r="G1898">
-        <v>0.0410958904109589</v>
-      </c>
-      <c r="H1898">
-        <v>875</v>
-      </c>
-      <c r="I1898">
-        <v>765</v>
-      </c>
-      <c r="J1898">
-        <v>28</v>
-      </c>
-      <c r="K1898">
-        <v>27.89</v>
-      </c>
-    </row>
-    <row r="1899" spans="1:11">
-      <c r="A1899">
-        <v>149</v>
-      </c>
-      <c r="B1899">
-        <v>109</v>
-      </c>
-      <c r="C1899">
-        <v>139</v>
-      </c>
-      <c r="D1899">
-        <v>193</v>
-      </c>
-      <c r="E1899">
-        <v>0.486146095717884</v>
-      </c>
-      <c r="F1899">
-        <v>1.29530201342282</v>
-      </c>
-      <c r="G1899">
-        <v>0.0402684563758389</v>
-      </c>
-      <c r="H1899">
-        <v>892</v>
-      </c>
-      <c r="I1899">
-        <v>780</v>
-      </c>
-      <c r="J1899">
-        <v>28</v>
-      </c>
-      <c r="K1899">
-        <v>28.7</v>
-      </c>
-    </row>
-    <row r="1900" spans="1:11">
-      <c r="A1900">
-        <v>159</v>
-      </c>
-      <c r="B1900">
-        <v>0</v>
-      </c>
-      <c r="C1900">
-        <v>187</v>
-      </c>
-      <c r="D1900">
-        <v>176</v>
-      </c>
-      <c r="E1900">
-        <v>0.508670520231214</v>
-      </c>
-      <c r="F1900">
-        <v>1.10691823899371</v>
-      </c>
-      <c r="G1900">
-        <v>0.0691823899371069</v>
-      </c>
-      <c r="H1900">
-        <v>990</v>
-      </c>
-      <c r="I1900">
-        <v>789</v>
-      </c>
-      <c r="J1900">
-        <v>28</v>
-      </c>
-      <c r="K1900">
-        <v>32.57</v>
-      </c>
-    </row>
-    <row r="1901" spans="1:11">
-      <c r="A1901">
-        <v>261</v>
-      </c>
-      <c r="B1901">
-        <v>78</v>
-      </c>
-      <c r="C1901">
-        <v>100</v>
-      </c>
-      <c r="D1901">
-        <v>201</v>
-      </c>
-      <c r="E1901">
-        <v>0.457858769931663</v>
-      </c>
-      <c r="F1901">
-        <v>0.770114942528736</v>
-      </c>
-      <c r="G1901">
-        <v>0.0344827586206896</v>
-      </c>
-      <c r="H1901">
-        <v>864</v>
-      </c>
-      <c r="I1901">
-        <v>761</v>
-      </c>
-      <c r="J1901">
-        <v>28</v>
-      </c>
-      <c r="K1901">
         <v>34.18</v>
-      </c>
-    </row>
-    <row r="1902" spans="1:11">
-      <c r="A1902">
-        <v>140</v>
-      </c>
-      <c r="B1902">
-        <v>1.4</v>
-      </c>
-      <c r="C1902">
-        <v>198.1</v>
-      </c>
-      <c r="D1902">
-        <v>174.9</v>
-      </c>
-      <c r="E1902">
-        <v>0.515169366715759</v>
-      </c>
-      <c r="F1902">
-        <v>1.24928571428571</v>
-      </c>
-      <c r="G1902">
-        <v>0.0314285714285714</v>
-      </c>
-      <c r="H1902">
-        <v>1049.9</v>
-      </c>
-      <c r="I1902">
-        <v>780.5</v>
-      </c>
-      <c r="J1902">
-        <v>28</v>
-      </c>
-      <c r="K1902">
-        <v>30.83</v>
-      </c>
-    </row>
-    <row r="1903" spans="1:11">
-      <c r="A1903">
-        <v>141.1</v>
-      </c>
-      <c r="B1903">
-        <v>0.6</v>
-      </c>
-      <c r="C1903">
-        <v>209.5</v>
-      </c>
-      <c r="D1903">
-        <v>188.8</v>
-      </c>
-      <c r="E1903">
-        <v>0.537585421412301</v>
-      </c>
-      <c r="F1903">
-        <v>1.33805811481219</v>
-      </c>
-      <c r="G1903">
-        <v>0.0326009922041106</v>
-      </c>
-      <c r="H1903">
-        <v>996.1</v>
-      </c>
-      <c r="I1903">
-        <v>789.2</v>
-      </c>
-      <c r="J1903">
-        <v>28</v>
-      </c>
-      <c r="K1903">
-        <v>30.43</v>
-      </c>
-    </row>
-    <row r="1904" spans="1:11">
-      <c r="A1904">
-        <v>140.1</v>
-      </c>
-      <c r="B1904">
-        <v>4.2</v>
-      </c>
-      <c r="C1904">
-        <v>215.9</v>
-      </c>
-      <c r="D1904">
-        <v>193.9</v>
-      </c>
-      <c r="E1904">
-        <v>0.538312048861744</v>
-      </c>
-      <c r="F1904">
-        <v>1.38401142041399</v>
-      </c>
-      <c r="G1904">
-        <v>0.033547466095646</v>
-      </c>
-      <c r="H1904">
-        <v>1049.5</v>
-      </c>
-      <c r="I1904">
-        <v>710.1</v>
-      </c>
-      <c r="J1904">
-        <v>28</v>
-      </c>
-      <c r="K1904">
-        <v>26.42</v>
-      </c>
-    </row>
-    <row r="1905" spans="1:11">
-      <c r="A1905">
-        <v>140.1</v>
-      </c>
-      <c r="B1905">
-        <v>11.8</v>
-      </c>
-      <c r="C1905">
-        <v>226.1</v>
-      </c>
-      <c r="D1905">
-        <v>207.8</v>
-      </c>
-      <c r="E1905">
-        <v>0.54973544973545</v>
-      </c>
-      <c r="F1905">
-        <v>1.48322626695218</v>
-      </c>
-      <c r="G1905">
-        <v>0.0349750178443969</v>
-      </c>
-      <c r="H1905">
-        <v>1020.9</v>
-      </c>
-      <c r="I1905">
-        <v>683.8</v>
-      </c>
-      <c r="J1905">
-        <v>28</v>
-      </c>
-      <c r="K1905">
-        <v>26.28</v>
-      </c>
-    </row>
-    <row r="1906" spans="1:11">
-      <c r="A1906">
-        <v>160.2</v>
-      </c>
-      <c r="B1906">
-        <v>0.3</v>
-      </c>
-      <c r="C1906">
-        <v>240</v>
-      </c>
-      <c r="D1906">
-        <v>233.5</v>
-      </c>
-      <c r="E1906">
-        <v>0.583021223470662</v>
-      </c>
-      <c r="F1906">
-        <v>1.45755305867665</v>
-      </c>
-      <c r="G1906">
-        <v>0.0574282147315855</v>
-      </c>
-      <c r="H1906">
-        <v>781</v>
-      </c>
-      <c r="I1906">
-        <v>841.1</v>
-      </c>
-      <c r="J1906">
-        <v>28</v>
-      </c>
-      <c r="K1906">
-        <v>36.19</v>
-      </c>
-    </row>
-    <row r="1907" spans="1:11">
-      <c r="A1907">
-        <v>140.2</v>
-      </c>
-      <c r="B1907">
-        <v>30.5</v>
-      </c>
-      <c r="C1907">
-        <v>239</v>
-      </c>
-      <c r="D1907">
-        <v>169.4</v>
-      </c>
-      <c r="E1907">
-        <v>0.413473273126678</v>
-      </c>
-      <c r="F1907">
-        <v>1.20827389443652</v>
-      </c>
-      <c r="G1907">
-        <v>0.0378031383737518</v>
-      </c>
-      <c r="H1907">
-        <v>1028.4</v>
-      </c>
-      <c r="I1907">
-        <v>742.7</v>
-      </c>
-      <c r="J1907">
-        <v>28</v>
-      </c>
-      <c r="K1907">
-        <v>36.32</v>
-      </c>
-    </row>
-    <row r="1908" spans="1:11">
-      <c r="A1908">
-        <v>140.2</v>
-      </c>
-      <c r="B1908">
-        <v>44.8</v>
-      </c>
-      <c r="C1908">
-        <v>234.9</v>
-      </c>
-      <c r="D1908">
-        <v>171.3</v>
-      </c>
-      <c r="E1908">
-        <v>0.40795427482734</v>
-      </c>
-      <c r="F1908">
-        <v>1.22182596291013</v>
-      </c>
-      <c r="G1908">
-        <v>0.0392296718972896</v>
-      </c>
-      <c r="H1908">
-        <v>1047.6</v>
-      </c>
-      <c r="I1908">
-        <v>704</v>
-      </c>
-      <c r="J1908">
-        <v>28</v>
-      </c>
-      <c r="K1908">
-        <v>33.78</v>
-      </c>
-    </row>
-    <row r="1909" spans="1:11">
-      <c r="A1909">
-        <v>140.5</v>
-      </c>
-      <c r="B1909">
-        <v>61.1</v>
-      </c>
-      <c r="C1909">
-        <v>238.9</v>
-      </c>
-      <c r="D1909">
-        <v>182.5</v>
-      </c>
-      <c r="E1909">
-        <v>0.414301929625426</v>
-      </c>
-      <c r="F1909">
-        <v>1.29893238434164</v>
-      </c>
-      <c r="G1909">
-        <v>0.0405693950177936</v>
-      </c>
-      <c r="H1909">
-        <v>1017.7</v>
-      </c>
-      <c r="I1909">
-        <v>681.4</v>
-      </c>
-      <c r="J1909">
-        <v>28</v>
-      </c>
-      <c r="K1909">
-        <v>30.97</v>
-      </c>
-    </row>
-    <row r="1910" spans="1:11">
-      <c r="A1910">
-        <v>143.3</v>
-      </c>
-      <c r="B1910">
-        <v>91.8</v>
-      </c>
-      <c r="C1910">
-        <v>239.8</v>
-      </c>
-      <c r="D1910">
-        <v>200.8</v>
-      </c>
-      <c r="E1910">
-        <v>0.422825858075384</v>
-      </c>
-      <c r="F1910">
-        <v>1.40125610607118</v>
-      </c>
-      <c r="G1910">
-        <v>0.0432658757850663</v>
-      </c>
-      <c r="H1910">
-        <v>964.8</v>
-      </c>
-      <c r="I1910">
-        <v>647.1</v>
-      </c>
-      <c r="J1910">
-        <v>28</v>
-      </c>
-      <c r="K1910">
-        <v>27.09</v>
-      </c>
-    </row>
-    <row r="1911" spans="1:11">
-      <c r="A1911">
-        <v>194.3</v>
-      </c>
-      <c r="B1911">
-        <v>0.3</v>
-      </c>
-      <c r="C1911">
-        <v>240</v>
-      </c>
-      <c r="D1911">
-        <v>234.2</v>
-      </c>
-      <c r="E1911">
-        <v>0.538886332259549</v>
-      </c>
-      <c r="F1911">
-        <v>1.20535254760679</v>
-      </c>
-      <c r="G1911">
-        <v>0.0458054554812146</v>
-      </c>
-      <c r="H1911">
-        <v>780.6</v>
-      </c>
-      <c r="I1911">
-        <v>811.3</v>
-      </c>
-      <c r="J1911">
-        <v>28</v>
-      </c>
-      <c r="K1911">
-        <v>38.46</v>
-      </c>
-    </row>
-    <row r="1912" spans="1:11">
-      <c r="A1912">
-        <v>150.4</v>
-      </c>
-      <c r="B1912">
-        <v>110.9</v>
-      </c>
-      <c r="C1912">
-        <v>239.7</v>
-      </c>
-      <c r="D1912">
-        <v>168.1</v>
-      </c>
-      <c r="E1912">
-        <v>0.335528942115768</v>
-      </c>
-      <c r="F1912">
-        <v>1.11768617021277</v>
-      </c>
-      <c r="G1912">
-        <v>0.043218085106383</v>
-      </c>
-      <c r="H1912">
-        <v>1000.2</v>
-      </c>
-      <c r="I1912">
-        <v>667.2</v>
-      </c>
-      <c r="J1912">
-        <v>28</v>
-      </c>
-      <c r="K1912">
-        <v>37.92</v>
-      </c>
-    </row>
-    <row r="1913" spans="1:11">
-      <c r="A1913">
-        <v>150.3</v>
-      </c>
-      <c r="B1913">
-        <v>111.4</v>
-      </c>
-      <c r="C1913">
-        <v>238.8</v>
-      </c>
-      <c r="D1913">
-        <v>167.3</v>
-      </c>
-      <c r="E1913">
-        <v>0.334265734265734</v>
-      </c>
-      <c r="F1913">
-        <v>1.11310711909514</v>
-      </c>
-      <c r="G1913">
-        <v>0.0432468396540253</v>
-      </c>
-      <c r="H1913">
-        <v>999.5</v>
-      </c>
-      <c r="I1913">
-        <v>670.5</v>
-      </c>
-      <c r="J1913">
-        <v>28</v>
-      </c>
-      <c r="K1913">
-        <v>38.19</v>
-      </c>
-    </row>
-    <row r="1914" spans="1:11">
-      <c r="A1914">
-        <v>155.4</v>
-      </c>
-      <c r="B1914">
-        <v>122.1</v>
-      </c>
-      <c r="C1914">
-        <v>240</v>
-      </c>
-      <c r="D1914">
-        <v>179.9</v>
-      </c>
-      <c r="E1914">
-        <v>0.347632850241546</v>
-      </c>
-      <c r="F1914">
-        <v>1.15765765765766</v>
-      </c>
-      <c r="G1914">
-        <v>0.0431145431145431</v>
-      </c>
-      <c r="H1914">
-        <v>966.8</v>
-      </c>
-      <c r="I1914">
-        <v>652.5</v>
-      </c>
-      <c r="J1914">
-        <v>28</v>
-      </c>
-      <c r="K1914">
-        <v>35.52</v>
-      </c>
-    </row>
-    <row r="1915" spans="1:11">
-      <c r="A1915">
-        <v>165.3</v>
-      </c>
-      <c r="B1915">
-        <v>143.2</v>
-      </c>
-      <c r="C1915">
-        <v>238.3</v>
-      </c>
-      <c r="D1915">
-        <v>200.4</v>
-      </c>
-      <c r="E1915">
-        <v>0.366495976591075</v>
-      </c>
-      <c r="F1915">
-        <v>1.21234119782214</v>
-      </c>
-      <c r="G1915">
-        <v>0.0429522081064731</v>
-      </c>
-      <c r="H1915">
-        <v>883.2</v>
-      </c>
-      <c r="I1915">
-        <v>652.6</v>
-      </c>
-      <c r="J1915">
-        <v>28</v>
-      </c>
-      <c r="K1915">
-        <v>32.84</v>
-      </c>
-    </row>
-    <row r="1916" spans="1:11">
-      <c r="A1916">
-        <v>303.8</v>
-      </c>
-      <c r="B1916">
-        <v>0.2</v>
-      </c>
-      <c r="C1916">
-        <v>239.8</v>
-      </c>
-      <c r="D1916">
-        <v>236.4</v>
-      </c>
-      <c r="E1916">
-        <v>0.434718646561236</v>
-      </c>
-      <c r="F1916">
-        <v>0.778143515470704</v>
-      </c>
-      <c r="G1916">
-        <v>0.0273206056616195</v>
-      </c>
-      <c r="H1916">
-        <v>780.1</v>
-      </c>
-      <c r="I1916">
-        <v>715.3</v>
-      </c>
-      <c r="J1916">
-        <v>28</v>
-      </c>
-      <c r="K1916">
-        <v>44.48</v>
-      </c>
-    </row>
-    <row r="1917" spans="1:11">
-      <c r="A1917">
-        <v>172</v>
-      </c>
-      <c r="B1917">
-        <v>162.1</v>
-      </c>
-      <c r="C1917">
-        <v>238.5</v>
-      </c>
-      <c r="D1917">
-        <v>166</v>
-      </c>
-      <c r="E1917">
-        <v>0.289905693328676</v>
-      </c>
-      <c r="F1917">
-        <v>0.965116279069767</v>
-      </c>
-      <c r="G1917">
-        <v>0.0430232558139535</v>
-      </c>
-      <c r="H1917">
-        <v>953.3</v>
-      </c>
-      <c r="I1917">
-        <v>641.4</v>
-      </c>
-      <c r="J1917">
-        <v>28</v>
-      </c>
-      <c r="K1917">
-        <v>41.54</v>
-      </c>
-    </row>
-    <row r="1918" spans="1:11">
-      <c r="A1918">
-        <v>172.8</v>
-      </c>
-      <c r="B1918">
-        <v>158.3</v>
-      </c>
-      <c r="C1918">
-        <v>239.5</v>
-      </c>
-      <c r="D1918">
-        <v>166.4</v>
-      </c>
-      <c r="E1918">
-        <v>0.291622853137049</v>
-      </c>
-      <c r="F1918">
-        <v>0.962962962962963</v>
-      </c>
-      <c r="G1918">
-        <v>0.0428240740740741</v>
-      </c>
-      <c r="H1918">
-        <v>952.6</v>
-      </c>
-      <c r="I1918">
-        <v>644.1</v>
-      </c>
-      <c r="J1918">
-        <v>28</v>
-      </c>
-      <c r="K1918">
-        <v>41.81</v>
-      </c>
-    </row>
-    <row r="1919" spans="1:11">
-      <c r="A1919">
-        <v>184.3</v>
-      </c>
-      <c r="B1919">
-        <v>153.4</v>
-      </c>
-      <c r="C1919">
-        <v>239.2</v>
-      </c>
-      <c r="D1919">
-        <v>179</v>
-      </c>
-      <c r="E1919">
-        <v>0.31027907782978</v>
-      </c>
-      <c r="F1919">
-        <v>0.971242539338036</v>
-      </c>
-      <c r="G1919">
-        <v>0.0406945198046663</v>
-      </c>
-      <c r="H1919">
-        <v>920.2</v>
-      </c>
-      <c r="I1919">
-        <v>640.9</v>
-      </c>
-      <c r="J1919">
-        <v>28</v>
-      </c>
-      <c r="K1919">
-        <v>41.01</v>
-      </c>
-    </row>
-    <row r="1920" spans="1:11">
-      <c r="A1920">
-        <v>215.6</v>
-      </c>
-      <c r="B1920">
-        <v>112.9</v>
-      </c>
-      <c r="C1920">
-        <v>239</v>
-      </c>
-      <c r="D1920">
-        <v>198.7</v>
-      </c>
-      <c r="E1920">
-        <v>0.350132158590308</v>
-      </c>
-      <c r="F1920">
-        <v>0.921614100185529</v>
-      </c>
-      <c r="G1920">
-        <v>0.0343228200371058</v>
-      </c>
-      <c r="H1920">
-        <v>884</v>
-      </c>
-      <c r="I1920">
-        <v>649.1</v>
-      </c>
-      <c r="J1920">
-        <v>28</v>
-      </c>
-      <c r="K1920">
-        <v>39.13</v>
-      </c>
-    </row>
-    <row r="1921" spans="1:11">
-      <c r="A1921">
-        <v>295.3</v>
-      </c>
-      <c r="B1921">
-        <v>0</v>
-      </c>
-      <c r="C1921">
-        <v>239.9</v>
-      </c>
-      <c r="D1921">
-        <v>236.2</v>
-      </c>
-      <c r="E1921">
-        <v>0.441330343796711</v>
-      </c>
-      <c r="F1921">
-        <v>0.799864544530985</v>
-      </c>
-      <c r="G1921">
-        <v>0.0281070098205215</v>
-      </c>
-      <c r="H1921">
-        <v>780.3</v>
-      </c>
-      <c r="I1921">
-        <v>722.9</v>
-      </c>
-      <c r="J1921">
-        <v>28</v>
-      </c>
-      <c r="K1921">
-        <v>44.08</v>
-      </c>
-    </row>
-    <row r="1922" spans="1:11">
-      <c r="A1922">
-        <v>248.3</v>
-      </c>
-      <c r="B1922">
-        <v>101</v>
-      </c>
-      <c r="C1922">
-        <v>239.1</v>
-      </c>
-      <c r="D1922">
-        <v>168.9</v>
-      </c>
-      <c r="E1922">
-        <v>0.287049626104691</v>
-      </c>
-      <c r="F1922">
-        <v>0.680225533628675</v>
-      </c>
-      <c r="G1922">
-        <v>0.0310108739428111</v>
-      </c>
-      <c r="H1922">
-        <v>954.2</v>
-      </c>
-      <c r="I1922">
-        <v>640.6</v>
-      </c>
-      <c r="J1922">
-        <v>28</v>
-      </c>
-      <c r="K1922">
-        <v>49.97</v>
-      </c>
-    </row>
-    <row r="1923" spans="1:11">
-      <c r="A1923">
-        <v>248</v>
-      </c>
-      <c r="B1923">
-        <v>101</v>
-      </c>
-      <c r="C1923">
-        <v>239.9</v>
-      </c>
-      <c r="D1923">
-        <v>169.1</v>
-      </c>
-      <c r="E1923">
-        <v>0.287145525556122</v>
-      </c>
-      <c r="F1923">
-        <v>0.681854838709677</v>
-      </c>
-      <c r="G1923">
-        <v>0.0310483870967742</v>
-      </c>
-      <c r="H1923">
-        <v>949.9</v>
-      </c>
-      <c r="I1923">
-        <v>644.1</v>
-      </c>
-      <c r="J1923">
-        <v>28</v>
-      </c>
-      <c r="K1923">
-        <v>50.23</v>
-      </c>
-    </row>
-    <row r="1924" spans="1:11">
-      <c r="A1924">
-        <v>258.8</v>
-      </c>
-      <c r="B1924">
-        <v>88</v>
-      </c>
-      <c r="C1924">
-        <v>239.6</v>
-      </c>
-      <c r="D1924">
-        <v>175.3</v>
-      </c>
-      <c r="E1924">
-        <v>0.298942701227831</v>
-      </c>
-      <c r="F1924">
-        <v>0.677357032457496</v>
-      </c>
-      <c r="G1924">
-        <v>0.0293663060278207</v>
-      </c>
-      <c r="H1924">
-        <v>938.9</v>
-      </c>
-      <c r="I1924">
-        <v>646</v>
-      </c>
-      <c r="J1924">
-        <v>28</v>
-      </c>
-      <c r="K1924">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="1925" spans="1:11">
-      <c r="A1925">
-        <v>297.1</v>
-      </c>
-      <c r="B1925">
-        <v>40.9</v>
-      </c>
-      <c r="C1925">
-        <v>239.9</v>
-      </c>
-      <c r="D1925">
-        <v>194</v>
-      </c>
-      <c r="E1925">
-        <v>0.335698217684721</v>
-      </c>
-      <c r="F1925">
-        <v>0.652978795018512</v>
-      </c>
-      <c r="G1925">
-        <v>0.0252440255806126</v>
-      </c>
-      <c r="H1925">
-        <v>908.9</v>
-      </c>
-      <c r="I1925">
-        <v>651.8</v>
-      </c>
-      <c r="J1925">
-        <v>28</v>
-      </c>
-      <c r="K1925">
-        <v>49.17</v>
-      </c>
-    </row>
-    <row r="1926" spans="1:11">
-      <c r="A1926">
-        <v>348.7</v>
-      </c>
-      <c r="B1926">
-        <v>0.1</v>
-      </c>
-      <c r="C1926">
-        <v>223.1</v>
-      </c>
-      <c r="D1926">
-        <v>208.5</v>
-      </c>
-      <c r="E1926">
-        <v>0.364574226263333</v>
-      </c>
-      <c r="F1926">
-        <v>0.597935187840551</v>
-      </c>
-      <c r="G1926">
-        <v>0.0275308287926584</v>
-      </c>
-      <c r="H1926">
-        <v>786.2</v>
-      </c>
-      <c r="I1926">
-        <v>758.1</v>
-      </c>
-      <c r="J1926">
-        <v>28</v>
-      </c>
-      <c r="K1926">
-        <v>48.77</v>
       </c>
     </row>
   </sheetData>
